--- a/public/templates/printed_books_template.xlsx
+++ b/public/templates/printed_books_template.xlsx
@@ -413,16 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -497,7 +489,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Introduction to Philippine politics &amp; governance (with basic constitutional provisions)</t>
+          <t>Introduction to Philippine politics &amp; governance</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -508,7 +500,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wiseman's Books Trading</t>
+          <t>Wiseman's Books</t>
         </is>
       </c>
     </row>
@@ -537,202 +529,6 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Rex Book Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>351 B489 Fil</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bihasa, Carmelo Rico S.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Introduction to public administration</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>C&amp;E Publishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>338.9 C112 Fil</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cabudol, Emerson G.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Economic development</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mindshapers</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>330.122 P75 Fil</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Poblador, Niceto S.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Strategy in the new age of capitalism : collaborative and inclusive approaches to value creation</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>UP Press</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>330.122 L61</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Li, Kui Wai</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Redefining capitalism in global economic development</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2017</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Academic Press</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>320.6 M764 Fil</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Montemayor, Jose C. Jr.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Policy (definition and its concept)</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mutya Publishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>321.02 M764 Fil</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Montemayor, Jose C., Jr.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Federalism : national and international perspective, are we ready?</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mutya Publishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>301 L297</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Lanuza, Gerry M.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Understanding culture, society, and politics</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vibal Group</t>
         </is>
       </c>
     </row>

--- a/public/templates/printed_books_template.xlsx
+++ b/public/templates/printed_books_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>Publisher</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +480,11 @@
           <t>Mutya Publishing</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Main Campus</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +513,11 @@
           <t>Wiseman's Books</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Main Campus</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,6 +544,11 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Rex Book Store</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PSU-Coron</t>
         </is>
       </c>
     </row>

--- a/public/templates/printed_books_template.xlsx
+++ b/public/templates/printed_books_template.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Printed Books" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Printed Books" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,157 +351,187 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Call No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Copies</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Publisher</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Campus</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Call No.</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Author</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Year</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Copies</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Publisher</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Barcode / Accession No.</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>320 V235 Fil</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Valenzuela, Edwin E.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Understanding basic concepts in political science</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="A2" t="str">
+        <v>320 V235 Fil</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Valenzuela, Edwin E.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Understanding basic concepts in political science</v>
+      </c>
+      <c r="D2">
         <v>2016</v>
       </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mutya Publishing</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Main Campus</t>
-        </is>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Mutya Publishing</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Main Campus</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2016-000123</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>320.9599 B145 Fil</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Baes, Aldrin P.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Introduction to Philippine politics &amp; governance</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Wiseman's Books</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Main Campus</t>
-        </is>
+      <c r="A3" t="str">
+        <v>320 V235 Fil</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Valenzuela, Edwin E.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Understanding basic concepts in political science</v>
+      </c>
+      <c r="D3">
+        <v>2016</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Mutya Publishing</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Main Campus</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2016-000124</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>320.9914 P289 Fil</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pawilen, R.A.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Philippine politics and governance</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="A4" t="str">
+        <v>320.9599 B145 Fil</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Baes, Aldrin P.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Introduction to Philippine politics &amp; governance</v>
+      </c>
+      <c r="D4">
+        <v>2024</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Wiseman's Books</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Main Campus</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>320.9914 P289 Fil</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Pawilen, R.A.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Philippine politics and governance</v>
+      </c>
+      <c r="D5">
         <v>2017</v>
       </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rex Book Store</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PSU-Coron</t>
-        </is>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Rex Book Store</v>
+      </c>
+      <c r="G5" t="str">
+        <v>PSU-Coron</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2017-000045</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
 </worksheet>
 </file>